--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
   <si>
     <t>引脚</t>
   </si>
@@ -172,34 +172,46 @@
     <t>7.4v</t>
   </si>
   <si>
-    <t>替换为PCO-PC3</t>
+    <t>替换为PG6、PG7、PG8、PD3</t>
   </si>
   <si>
     <t>用途</t>
   </si>
   <si>
-    <t>PC0</t>
+    <t>PG6</t>
   </si>
   <si>
     <t>丝杆上限位</t>
   </si>
   <si>
-    <t>PC1</t>
+    <t>LIFT_UP_LIMIT</t>
+  </si>
+  <si>
+    <t>PG7</t>
   </si>
   <si>
     <t>丝杆下限位</t>
   </si>
   <si>
-    <t>PC2</t>
+    <t>LIFT_DOWN_LIMIT</t>
+  </si>
+  <si>
+    <t>PG8</t>
   </si>
   <si>
     <t>机械臂平移前限位</t>
   </si>
   <si>
-    <t>PC3</t>
+    <t>SLIDE_FRONT_LIMIT</t>
+  </si>
+  <si>
+    <t>PD3</t>
   </si>
   <si>
     <t>机械臂平移后限位</t>
+  </si>
+  <si>
+    <t>SLIDE_REAR_LIMIT</t>
   </si>
   <si>
     <t>额外空闲gpio</t>
@@ -1535,70 +1547,82 @@
       <c r="I20" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="21" spans="6:10">
       <c r="H21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="J21" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="6:10">
       <c r="H22" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="J22" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" ht="28.8" spans="6:10">
       <c r="H23" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="J23" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="6:10">
       <c r="F26" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="6:10">
       <c r="G27" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I27" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="6:10">
       <c r="G28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="6:10">
       <c r="G29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H29" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1634,16 +1658,16 @@
     <row r="1" ht="44" customHeight="1"/>
     <row r="4" spans="3:7">
       <c r="C4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="3:7">
@@ -1651,13 +1675,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="3:7">
@@ -1665,13 +1689,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="3:7">
@@ -1679,13 +1703,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1693,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="3:7">
@@ -1701,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="3:7">
@@ -1709,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -43,7 +43,7 @@
     <t>其他电子硬件</t>
   </si>
   <si>
-    <t>PC调试</t>
+    <t>PC调试/DAPLink调试</t>
   </si>
   <si>
     <t>PA9</t>

--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -29,7 +29,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="98">
+  <si>
+    <t>STM32F407</t>
+  </si>
+  <si>
+    <t>Jetson</t>
+  </si>
   <si>
     <t>引脚</t>
   </si>
@@ -64,6 +70,9 @@
     <t>可以圆头也可以插杜邦线</t>
   </si>
   <si>
+    <t>USB</t>
+  </si>
+  <si>
     <t>PA10</t>
   </si>
   <si>
@@ -73,6 +82,21 @@
     <t>RS232转TTL</t>
   </si>
   <si>
+    <t>下位机通信</t>
+  </si>
+  <si>
+    <t>Pin8</t>
+  </si>
+  <si>
+    <t>UART1_TXD</t>
+  </si>
+  <si>
+    <t>摄像头QR</t>
+  </si>
+  <si>
+    <t>/dev/video0</t>
+  </si>
+  <si>
     <t>WIT陀螺仪</t>
   </si>
   <si>
@@ -91,12 +115,36 @@
     <t>6-9或8-24</t>
   </si>
   <si>
+    <t>Pin10</t>
+  </si>
+  <si>
+    <t>UART1_RXD</t>
+  </si>
+  <si>
+    <t>摄像头Vision</t>
+  </si>
+  <si>
+    <t>/dev/video1</t>
+  </si>
+  <si>
     <t>PA3</t>
   </si>
   <si>
     <t>陀螺仪</t>
   </si>
   <si>
+    <t>补光灯</t>
+  </si>
+  <si>
+    <t>Pin33</t>
+  </si>
+  <si>
+    <t>GPIO_13用于pwm控制补光灯亮度</t>
+  </si>
+  <si>
+    <t>雷达（备选）</t>
+  </si>
+  <si>
     <t>步进电机扩展板</t>
   </si>
   <si>
@@ -112,6 +160,9 @@
     <t>5-24v</t>
   </si>
   <si>
+    <t>这个只给vision使用，要求只能向下打光</t>
+  </si>
+  <si>
     <t>PB11</t>
   </si>
   <si>
@@ -140,9 +191,6 @@
   </si>
   <si>
     <t>PD2</t>
-  </si>
-  <si>
-    <t>Jetson</t>
   </si>
   <si>
     <t>PC6</t>
@@ -287,9 +335,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -774,139 +829,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -914,7 +972,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1274,7 +1332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F4:O29"/>
+  <dimension ref="F2:V29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="6" max="6" width="24.009009009009" customWidth="1"/>
@@ -1284,349 +1342,423 @@
     <col min="10" max="10" width="11.7747747747748" customWidth="1"/>
     <col min="13" max="13" width="24.8378378378378" customWidth="1"/>
     <col min="15" max="15" width="33.7207207207207" customWidth="1"/>
+    <col min="17" max="17" width="16.3873873873874" customWidth="1"/>
+    <col min="18" max="18" width="9.71171171171171" customWidth="1"/>
+    <col min="19" max="19" width="32.2702702702703" customWidth="1"/>
+    <col min="21" max="21" width="15.2702702702703" customWidth="1"/>
+    <col min="22" max="22" width="14.9189189189189" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="6:15">
+    <row r="2" spans="6:22">
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="6:22">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="Q3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="6:22">
       <c r="G4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="6:15">
-      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="6:22">
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="G5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N5">
         <v>12</v>
       </c>
       <c r="O5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="6:15">
-      <c r="F6" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="R5" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>3</v>
+      </c>
+      <c r="U5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="6:22">
+      <c r="F6" s="2"/>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I6" s="2"/>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N6">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="7" spans="6:15">
-      <c r="F7" s="1" t="s">
-        <v>14</v>
+      <c r="Q6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="6:22">
+      <c r="F7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O7">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="8" spans="6:15">
-      <c r="F8" s="1"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" t="s">
+        <v>29</v>
+      </c>
+      <c r="U7" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="6:22">
+      <c r="F8" s="2"/>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I8" s="2"/>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="6:15">
-      <c r="F9" s="1" t="s">
-        <v>22</v>
+      <c r="Q8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8"/>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="6:22">
+      <c r="F9" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="J9">
         <v>12</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="O9">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="10" spans="6:15">
-      <c r="F10" s="1"/>
+      <c r="S9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="6:22">
+      <c r="F10" s="2"/>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I10" s="2"/>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="6:15">
-      <c r="F11" s="1" t="s">
-        <v>29</v>
+    <row r="11" spans="6:22">
+      <c r="F11" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="6:15">
-      <c r="F12" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="6:22">
+      <c r="F12" s="2"/>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="6:15">
-      <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="6:22">
+      <c r="F13" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="J13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="6:15">
-      <c r="F14" s="1"/>
+    <row r="14" spans="6:22">
+      <c r="F14" s="2"/>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="6:15">
-      <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="6:22">
+      <c r="F15" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="K15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="6:22">
+      <c r="F16" s="2"/>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="6:10">
+      <c r="F17" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="6:15">
-      <c r="F16" s="1"/>
-      <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="6:10">
-      <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>43</v>
+      <c r="G17" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="6:10">
       <c r="G18" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="6:10">
-      <c r="H19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>48</v>
+      <c r="H19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="6:10">
-      <c r="H20" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>50</v>
+      <c r="H20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="6:10">
-      <c r="H21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>53</v>
+      <c r="H21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="6:10">
-      <c r="H22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>56</v>
+      <c r="H22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="J22" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="28.8" spans="6:10">
-      <c r="H23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>59</v>
+      <c r="H23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="J23" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="6:10">
-      <c r="F26" s="1" t="s">
-        <v>61</v>
+      <c r="F26" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="6:10">
       <c r="G27" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="6:10">
       <c r="G28" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="6:10">
       <c r="G29" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F9:F10"/>
@@ -1639,6 +1771,9 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="I15:I16"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="F2:G3"/>
+    <mergeCell ref="Q3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1658,16 +1793,16 @@
     <row r="1" ht="44" customHeight="1"/>
     <row r="4" spans="3:7">
       <c r="C4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="3:7">
@@ -1675,13 +1810,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="3:7">
@@ -1689,13 +1824,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="3:7">
@@ -1703,13 +1838,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1717,7 +1852,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="3:7">
@@ -1725,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="3:7">
@@ -1733,7 +1868,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\littleCar2\zhengdian\4-29\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27526" windowHeight="14964"/>
   </bookViews>
@@ -136,10 +141,10 @@
     <t>补光灯</t>
   </si>
   <si>
-    <t>Pin33</t>
-  </si>
-  <si>
-    <t>GPIO_13用于pwm控制补光灯亮度</t>
+    <t>Pin32</t>
+  </si>
+  <si>
+    <t>GPIO_07用于pwm控制补光灯亮度</t>
   </si>
   <si>
     <t>雷达（备选）</t>
@@ -1511,7 +1516,6 @@
       <c r="S8" t="s">
         <v>36</v>
       </c>
-      <c r="T8"/>
       <c r="U8" t="s">
         <v>37</v>
       </c>
